--- a/backend/data/financials_by_company/1708.HK.xlsx
+++ b/backend/data/financials_by_company/1708.HK.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE5"/>
+  <dimension ref="A1:BE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -707,62 +707,26 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-39236707.20136</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.09515700000000001</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-18963499.98</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-412334709</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-412334709</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-420592151.7</v>
-      </c>
-      <c r="H2" t="n">
-        <v>6630126.19</v>
-      </c>
-      <c r="I2" t="n">
-        <v>375625654.92</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-431298208.98</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-437928335.17</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-26899532.12</v>
-      </c>
-      <c r="M2" t="n">
-        <v>27069007.64</v>
-      </c>
-      <c r="N2" t="n">
-        <v>693054.5699999999</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-47494149.90136</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-420592151.7</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>465381169.5</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1667738.93</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-409946339.66</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
         <v>792058500</v>
       </c>
@@ -770,167 +734,113 @@
         <v>792058500</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.531</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.531</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-420592151.7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-420592151.7</v>
-      </c>
-      <c r="Z2" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="n">
+        <v>-3332548.02</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="n">
         <v>0</v>
       </c>
-      <c r="AA2" t="n">
-        <v>-420592151.7</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>157243.53</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-420749395.23</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="n">
-        <v>-420749395.23</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-44247947.58</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-464997342.81</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-1545647.86</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-405101210.68</v>
-      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>49910165.11</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>353302474.28</v>
-      </c>
+        <v>-7883873.6</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>1888571.29</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-26899532.12</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>523579.05</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>27069007.64</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>693054.5699999999</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-25509455.91</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>89755514.58</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>3826249.15</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>6166308.97</v>
-      </c>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="n">
-        <v>6166308.97</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>19155472.26</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>24776178.16</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>10803044.71</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>13973133.45</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>1667738.93</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>64246058.67</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>375625654.92</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>439871713.59</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>439871713.59</v>
-      </c>
+        <v>832.6</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="n">
+        <v>761599.95</v>
+      </c>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-29519.980899</v>
+        <v>-2632954.262547</v>
       </c>
       <c r="C3" t="n">
-        <v>0.010461</v>
+        <v>0.013562</v>
       </c>
       <c r="D3" t="n">
-        <v>76755281.70999999</v>
+        <v>-50823240.64</v>
       </c>
       <c r="E3" t="n">
-        <v>-2821802.67</v>
+        <v>-194146341.04</v>
       </c>
       <c r="F3" t="n">
-        <v>-2821802.67</v>
+        <v>-194146341.04</v>
       </c>
       <c r="G3" t="n">
-        <v>1994964.77</v>
+        <v>-273526467.22</v>
       </c>
       <c r="H3" t="n">
-        <v>38139654.11</v>
+        <v>17270476.3</v>
       </c>
       <c r="I3" t="n">
-        <v>406102733.27</v>
+        <v>483429208.33</v>
       </c>
       <c r="J3" t="n">
-        <v>73933479.04000001</v>
+        <v>-244969581.68</v>
       </c>
       <c r="K3" t="n">
-        <v>35793824.93</v>
+        <v>-262240057.98</v>
       </c>
       <c r="L3" t="n">
-        <v>-32743422.78</v>
+        <v>-36830549.25</v>
       </c>
       <c r="M3" t="n">
-        <v>34053010.53</v>
+        <v>42758466.41</v>
       </c>
       <c r="N3" t="n">
-        <v>1249797.61</v>
+        <v>5672499.57</v>
       </c>
       <c r="O3" t="n">
-        <v>4787247.459101</v>
+        <v>-82013080.44254699</v>
       </c>
       <c r="P3" t="n">
-        <v>1994964.77</v>
+        <v>-273526467.22</v>
       </c>
       <c r="Q3" t="n">
-        <v>499630253.29</v>
+        <v>590052690.53</v>
       </c>
       <c r="R3" t="n">
-        <v>1075913.47</v>
+        <v>1164365.61</v>
       </c>
       <c r="S3" t="n">
-        <v>9366258.35</v>
+        <v>-307745303.59</v>
       </c>
       <c r="T3" t="n">
         <v>792058500</v>
@@ -939,169 +849,169 @@
         <v>792058500</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003</v>
+        <v>-0.345</v>
       </c>
       <c r="W3" t="n">
-        <v>0.003</v>
+        <v>-0.345</v>
       </c>
       <c r="X3" t="n">
-        <v>1994964.77</v>
+        <v>-273526467.22</v>
       </c>
       <c r="Y3" t="n">
-        <v>1994964.77</v>
+        <v>-273526467.22</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1994964.77</v>
+        <v>-273526467.22</v>
       </c>
       <c r="AB3" t="n">
-        <v>272361.71</v>
+        <v>27335758.95</v>
       </c>
       <c r="AC3" t="n">
-        <v>1722603.06</v>
+        <v>-300862226.17</v>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>1722603.06</v>
+        <v>-300862226.17</v>
       </c>
       <c r="AF3" t="n">
-        <v>18211.34</v>
+        <v>-4136298.22</v>
       </c>
       <c r="AG3" t="n">
-        <v>1740814.4</v>
+        <v>-304998524.39</v>
       </c>
       <c r="AH3" t="n">
-        <v>-7627913.95</v>
+        <v>3035592.27</v>
       </c>
       <c r="AI3" t="n">
-        <v>12389708.64</v>
+        <v>-195254173.89</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-194541.84</v>
+        <v>1312184.01</v>
       </c>
       <c r="AK3" t="n">
-        <v>-12195196.8</v>
+        <v>193873987.59</v>
       </c>
       <c r="AL3" t="n">
-        <v>30</v>
+        <v>68002.28999999999</v>
       </c>
       <c r="AM3" t="n">
-        <v>-32743422.78</v>
+        <v>-36830549.25</v>
       </c>
       <c r="AN3" t="n">
-        <v>-59790.14</v>
+        <v>-255417.59</v>
       </c>
       <c r="AO3" t="n">
-        <v>34053010.53</v>
+        <v>42758466.41</v>
       </c>
       <c r="AP3" t="n">
-        <v>1249797.61</v>
+        <v>5672499.57</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-6089183.74</v>
+        <v>-77387496.52</v>
       </c>
       <c r="AR3" t="n">
-        <v>93527520.02</v>
+        <v>106623482.2</v>
       </c>
       <c r="AS3" t="n">
-        <v>4421795.59</v>
+        <v>5842259.59</v>
       </c>
       <c r="AT3" t="n">
-        <v>13515073.76</v>
+        <v>17270476.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>706506.28</v>
+        <v>816569.17</v>
       </c>
       <c r="AV3" t="n">
-        <v>13515073.76</v>
+        <v>16453907.13</v>
       </c>
       <c r="AW3" t="n">
-        <v>23171313.59</v>
+        <v>23139593.4</v>
       </c>
       <c r="AX3" t="n">
-        <v>24308668.96</v>
+        <v>25084882.61</v>
       </c>
       <c r="AY3" t="n">
-        <v>11125750.67</v>
+        <v>11240431.64</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13182918.29</v>
+        <v>13844450.97</v>
       </c>
       <c r="BA3" t="n">
-        <v>1075913.47</v>
+        <v>1164365.61</v>
       </c>
       <c r="BB3" t="n">
-        <v>87438336.28</v>
+        <v>29235985.68</v>
       </c>
       <c r="BC3" t="n">
-        <v>406102733.27</v>
+        <v>483429208.33</v>
       </c>
       <c r="BD3" t="n">
-        <v>493541069.55</v>
+        <v>512665194.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>493541069.55</v>
+        <v>512665194.01</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-2632954.262547</v>
+        <v>-29519.980899</v>
       </c>
       <c r="C4" t="n">
-        <v>0.013562</v>
+        <v>0.010461</v>
       </c>
       <c r="D4" t="n">
-        <v>-10892982.19</v>
+        <v>52130701.36</v>
       </c>
       <c r="E4" t="n">
-        <v>-194146341.04</v>
+        <v>-2821802.67</v>
       </c>
       <c r="F4" t="n">
-        <v>-194146341.04</v>
+        <v>-2821802.67</v>
       </c>
       <c r="G4" t="n">
-        <v>-273526467.22</v>
+        <v>1994964.77</v>
       </c>
       <c r="H4" t="n">
-        <v>57200734.75</v>
+        <v>13515073.76</v>
       </c>
       <c r="I4" t="n">
-        <v>483429208.33</v>
+        <v>406102733.27</v>
       </c>
       <c r="J4" t="n">
-        <v>-205039323.23</v>
+        <v>49308898.69</v>
       </c>
       <c r="K4" t="n">
-        <v>-262240057.98</v>
+        <v>35793824.93</v>
       </c>
       <c r="L4" t="n">
-        <v>-36830549.25</v>
+        <v>-32743422.78</v>
       </c>
       <c r="M4" t="n">
-        <v>42758466.41</v>
+        <v>34053010.53</v>
       </c>
       <c r="N4" t="n">
-        <v>5672499.57</v>
+        <v>1249797.61</v>
       </c>
       <c r="O4" t="n">
-        <v>-82013080.44254699</v>
+        <v>4787247.459101</v>
       </c>
       <c r="P4" t="n">
-        <v>-273526467.22</v>
+        <v>1994964.77</v>
       </c>
       <c r="Q4" t="n">
-        <v>590052690.53</v>
+        <v>499630253.29</v>
       </c>
       <c r="R4" t="n">
-        <v>1164365.61</v>
+        <v>1075913.47</v>
       </c>
       <c r="S4" t="n">
-        <v>-307745303.59</v>
+        <v>9366258.35</v>
       </c>
       <c r="T4" t="n">
         <v>792058500</v>
@@ -1110,169 +1020,169 @@
         <v>792058500</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.345</v>
+        <v>0.003</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.345</v>
+        <v>0.003</v>
       </c>
       <c r="X4" t="n">
-        <v>-273526467.22</v>
+        <v>1994964.77</v>
       </c>
       <c r="Y4" t="n">
-        <v>-273526467.22</v>
+        <v>1994964.77</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-273526467.22</v>
+        <v>1994964.77</v>
       </c>
       <c r="AB4" t="n">
-        <v>27335758.95</v>
+        <v>272361.71</v>
       </c>
       <c r="AC4" t="n">
-        <v>-300862226.17</v>
+        <v>1722603.06</v>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>-300862226.17</v>
+        <v>1722603.06</v>
       </c>
       <c r="AF4" t="n">
-        <v>-4136298.22</v>
+        <v>18211.34</v>
       </c>
       <c r="AG4" t="n">
-        <v>-304998524.39</v>
+        <v>1740814.4</v>
       </c>
       <c r="AH4" t="n">
-        <v>3035592.27</v>
+        <v>-7627913.95</v>
       </c>
       <c r="AI4" t="n">
-        <v>-195254173.89</v>
+        <v>12389708.64</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1312184.01</v>
+        <v>-194541.84</v>
       </c>
       <c r="AK4" t="n">
-        <v>193873987.59</v>
+        <v>-12195196.8</v>
       </c>
       <c r="AL4" t="n">
-        <v>68002.28999999999</v>
+        <v>30</v>
       </c>
       <c r="AM4" t="n">
-        <v>-36830549.25</v>
+        <v>-32743422.78</v>
       </c>
       <c r="AN4" t="n">
-        <v>-255417.59</v>
+        <v>-59790.14</v>
       </c>
       <c r="AO4" t="n">
-        <v>42758466.41</v>
+        <v>34053010.53</v>
       </c>
       <c r="AP4" t="n">
-        <v>5672499.57</v>
+        <v>1249797.61</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-77387496.52</v>
+        <v>-6089183.74</v>
       </c>
       <c r="AR4" t="n">
-        <v>106623482.2</v>
+        <v>93527520.02</v>
       </c>
       <c r="AS4" t="n">
-        <v>5842259.59</v>
+        <v>4421795.59</v>
       </c>
       <c r="AT4" t="n">
-        <v>17270476.3</v>
+        <v>13515073.76</v>
       </c>
       <c r="AU4" t="n">
-        <v>816569.17</v>
+        <v>706506.28</v>
       </c>
       <c r="AV4" t="n">
-        <v>16453907.13</v>
+        <v>13515073.76</v>
       </c>
       <c r="AW4" t="n">
-        <v>23139593.4</v>
+        <v>23171313.59</v>
       </c>
       <c r="AX4" t="n">
-        <v>25084882.61</v>
+        <v>24308668.96</v>
       </c>
       <c r="AY4" t="n">
-        <v>11240431.64</v>
+        <v>11125750.67</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13844450.97</v>
+        <v>13182918.29</v>
       </c>
       <c r="BA4" t="n">
-        <v>1164365.61</v>
+        <v>1075913.47</v>
       </c>
       <c r="BB4" t="n">
-        <v>29235985.68</v>
+        <v>87438336.28</v>
       </c>
       <c r="BC4" t="n">
-        <v>483429208.33</v>
+        <v>406102733.27</v>
       </c>
       <c r="BD4" t="n">
-        <v>512665194.01</v>
+        <v>493541069.55</v>
       </c>
       <c r="BE4" t="n">
-        <v>512665194.01</v>
+        <v>493541069.55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-6877575.5775</v>
+        <v>-39236707.20136</v>
       </c>
       <c r="C5" t="n">
-        <v>0.25</v>
+        <v>0.09515700000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>83163854.61</v>
+        <v>-18963499.98</v>
       </c>
       <c r="E5" t="n">
-        <v>-27510302.31</v>
+        <v>-412334709</v>
       </c>
       <c r="F5" t="n">
-        <v>-27510302.31</v>
+        <v>-412334709</v>
       </c>
       <c r="G5" t="n">
-        <v>-59244735.65</v>
+        <v>-420592151.7</v>
       </c>
       <c r="H5" t="n">
-        <v>50601805.37</v>
+        <v>6630126.19</v>
       </c>
       <c r="I5" t="n">
-        <v>744568376.45</v>
+        <v>375625654.92</v>
       </c>
       <c r="J5" t="n">
-        <v>55653552.3</v>
+        <v>-431298208.98</v>
       </c>
       <c r="K5" t="n">
-        <v>5051746.93</v>
+        <v>-437928335.17</v>
       </c>
       <c r="L5" t="n">
-        <v>-58979233.02</v>
+        <v>-26899532.12</v>
       </c>
       <c r="M5" t="n">
-        <v>59758364.88</v>
+        <v>27069007.64</v>
       </c>
       <c r="N5" t="n">
-        <v>1894057.79</v>
+        <v>693054.5699999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-38612008.9175</v>
+        <v>-47494149.90136</v>
       </c>
       <c r="P5" t="n">
-        <v>-59244735.65</v>
+        <v>-420592151.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>883335561.55</v>
+        <v>465381169.5</v>
       </c>
       <c r="R5" t="n">
-        <v>800155.23</v>
+        <v>1667738.93</v>
       </c>
       <c r="S5" t="n">
-        <v>-54757098.35</v>
+        <v>-409946339.66</v>
       </c>
       <c r="T5" t="n">
         <v>792058500</v>
@@ -1281,112 +1191,263 @@
         <v>792058500</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.531</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.531</v>
       </c>
       <c r="X5" t="n">
-        <v>-59244735.65</v>
+        <v>-420592151.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>-59244735.65</v>
+        <v>-420592151.7</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-59244735.65</v>
+        <v>-420592151.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>-3332548.02</v>
+        <v>157243.53</v>
       </c>
       <c r="AC5" t="n">
-        <v>-55912187.63</v>
-      </c>
-      <c r="AD5" t="n">
+        <v>-420749395.23</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="n">
+        <v>-420749395.23</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-44247947.58</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-464997342.81</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-1545647.86</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-405101210.68</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>49910165.11</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>353302474.28</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1888571.29</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-26899532.12</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>523579.05</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>27069007.64</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>693054.5699999999</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-25509455.91</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>89755514.58</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>3826249.15</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6166308.97</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="n">
+        <v>6166308.97</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>19155472.26</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>24776178.16</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>10803044.71</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>13973133.45</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1667738.93</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>64246058.67</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>375625654.92</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>439871713.59</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>439871713.59</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-4397299.815</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D6" t="n">
+        <v>17270949.34</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-17589199.26</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-17589199.26</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-73124665.33</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1922519.59</v>
+      </c>
+      <c r="I6" t="n">
+        <v>436476787.59</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-318249.92</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-2240769.51</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-23112074.44</v>
+      </c>
+      <c r="M6" t="n">
+        <v>23255515.1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>364726.62</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-59932765.885</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-73124665.33</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>515190098.93</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1507154.76</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-23003028.27</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>-73124665.33</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-73124665.33</v>
+      </c>
+      <c r="Z6" t="n">
         <v>0</v>
       </c>
-      <c r="AE5" t="n">
-        <v>-55912187.63</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1205569.68</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-54706617.95</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>51313</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-38658674.81</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-7883873.6</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>46541715.81</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>832.6</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>-58979233.02</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1114925.93</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>59758364.88</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1894057.79</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>30678194</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>138767185.1</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>6234277.99</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>15306785.75</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>761599.95</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>14545185.8</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>48556855.68</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>51047712.45</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>38544136.51</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>12503575.94</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>800155.23</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>169445379.1</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>744568376.45</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>914013755.55</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>914013755.55</v>
+      <c r="AA6" t="n">
+        <v>-73124665.33</v>
+      </c>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>-73124665.33</v>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>-73124665.33</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>47628380.72</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-25496284.61</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-2037970.61</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-22227153.44</v>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="n">
+        <v>22227153.44</v>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="n">
+        <v>-23112074.44</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>221285.96</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>23255515.1</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>364726.62</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-11234948.47</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>78713311.34</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4315447.24</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1644376.07</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="n">
+        <v>1644376.07</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>23567843.41</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>17293649.92</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9062195.68</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>8231454.24</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1507154.76</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>67478362.87</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>436476787.59</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>503955150.46</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>503955150.46</v>
       </c>
     </row>
   </sheetData>
@@ -1400,7 +1461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CD5"/>
+  <dimension ref="A1:CD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1812,217 +1873,137 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>792058500</v>
-      </c>
-      <c r="C2" t="n">
-        <v>792058500</v>
-      </c>
-      <c r="D2" t="n">
-        <v>313569459.95</v>
-      </c>
-      <c r="E2" t="n">
-        <v>586125708.89</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1204986028.88</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1796061096.03</v>
-      </c>
-      <c r="H2" t="n">
-        <v>562310758.33</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1204986028.88</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
-        <v>1209935387.14</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1280785387.14</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1218604669.18</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>8669282.039999999</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1209935387.14</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="n">
-        <v>119155929.9</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>792058500</v>
-      </c>
-      <c r="T2" t="n">
-        <v>792058500</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="n">
-        <v>1167687754.35</v>
-      </c>
-      <c r="W2" t="n">
-        <v>105872093.53</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="n">
-        <v>1021907.98</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>34000185.55</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>70850000</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="n">
-        <v>70850000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1061815660.82</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>641173.4</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>515275708.89</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="n">
-        <v>515275708.89</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>523985.42</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>434976008.06</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>39505193.84</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="n">
-        <v>4613924.82</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>390856889.4</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>2386292423.53</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>762166004.38</v>
-      </c>
+        <v>40095532.09</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>103269821.12</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>1000000.02</v>
+        <v>23665787.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>98371.14999999999</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>125448113.68</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>145531388.15</v>
-      </c>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="n">
-        <v>42712749.75</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>102818638.4</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>10154577.39</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="n">
-        <v>422191100</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>4949358.26</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>4949358.26</v>
-      </c>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="n">
-        <v>52793095.73</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>-263994552.34</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>316787648.07</v>
-      </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="n">
-        <v>88883016.92</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>172265301.33</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>55639329.82</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>1624126419.15</v>
-      </c>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="inlineStr"/>
-      <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="n">
-        <v>15754991.57</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>5607358.59</v>
-      </c>
-      <c r="BR2" t="inlineStr"/>
-      <c r="BS2" t="inlineStr"/>
-      <c r="BT2" t="inlineStr"/>
-      <c r="BU2" t="n">
-        <v>1087125745.32</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>38237638.46</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>187805300.27</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>-277247227.04</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>465052527.31</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>289595384.94</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>17039136</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>272556248.94</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>259429791.43</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>13126457.51</v>
-      </c>
+        <v>620319.39</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="n">
+        <v>5728742.53</v>
+      </c>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="n">
+        <v>74216262.59999999</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>428077500</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>19435145.68</v>
+      </c>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="n">
+        <v>70378727.17</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>26158324.47</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>14513.27</v>
+      </c>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr"/>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="inlineStr"/>
+      <c r="CD2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>792058500</v>
@@ -2031,42 +2012,46 @@
         <v>792058500</v>
       </c>
       <c r="D3" t="n">
-        <v>318737557.12</v>
+        <v>350262885.44</v>
       </c>
       <c r="E3" t="n">
-        <v>685839799.67</v>
+        <v>823140241.64</v>
       </c>
       <c r="F3" t="n">
-        <v>1619818899.36</v>
+        <v>1538549712.16</v>
       </c>
       <c r="G3" t="n">
-        <v>2310178527.34</v>
+        <v>2372085574.82</v>
       </c>
       <c r="H3" t="n">
-        <v>1014399426.31</v>
+        <v>525645455.64</v>
       </c>
       <c r="I3" t="n">
-        <v>1619818899.36</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
+        <v>1538549712.16</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
       <c r="K3" t="n">
-        <v>1624338727.67</v>
+        <v>1548945333.18</v>
       </c>
       <c r="L3" t="n">
-        <v>1702588727.67</v>
+        <v>1636977784.96</v>
       </c>
       <c r="M3" t="n">
-        <v>1633165253.24</v>
+        <v>1558592307.71</v>
       </c>
       <c r="N3" t="n">
-        <v>8826525.57</v>
+        <v>9646974.529999999</v>
       </c>
       <c r="O3" t="n">
-        <v>1624338727.67</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
+        <v>1548945333.18</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q3" t="n">
-        <v>539748081.6</v>
+        <v>536999877.42</v>
       </c>
       <c r="R3" t="n">
         <v>80999419.73</v>
@@ -2077,160 +2062,190 @@
       <c r="T3" t="n">
         <v>792058500</v>
       </c>
-      <c r="U3" t="inlineStr"/>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
       <c r="V3" t="n">
-        <v>1241287401.51</v>
+        <v>1439702696.99</v>
       </c>
       <c r="W3" t="n">
-        <v>114859211.49</v>
-      </c>
-      <c r="X3" t="inlineStr"/>
+        <v>111677521.78</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
       <c r="Y3" t="n">
-        <v>126451.87</v>
+        <v>6935213.17</v>
       </c>
       <c r="Z3" t="n">
-        <v>36482759.62</v>
+        <v>16709856.83</v>
       </c>
       <c r="AA3" t="n">
-        <v>78250000</v>
-      </c>
-      <c r="AB3" t="inlineStr"/>
+        <v>88032451.78</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
       <c r="AC3" t="n">
-        <v>78250000</v>
+        <v>88032451.78</v>
       </c>
       <c r="AD3" t="n">
-        <v>1126428190.02</v>
+        <v>1328025175.21</v>
       </c>
       <c r="AE3" t="n">
-        <v>1700000</v>
+        <v>4923951.9</v>
       </c>
       <c r="AF3" t="n">
-        <v>607589799.67</v>
+        <v>735107789.86</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>607589799.67</v>
+        <v>735107789.86</v>
       </c>
       <c r="AI3" t="n">
-        <v>221603.85</v>
+        <v>226323.85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>459335195.1</v>
+        <v>516803430.97</v>
       </c>
       <c r="AK3" t="n">
-        <v>38482826.87</v>
-      </c>
-      <c r="AL3" t="inlineStr"/>
+        <v>38940006.97</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
       <c r="AM3" t="n">
-        <v>6010260.76</v>
+        <v>7930534.13</v>
       </c>
       <c r="AN3" t="n">
-        <v>414842107.47</v>
+        <v>469932889.87</v>
       </c>
       <c r="AO3" t="n">
-        <v>2874452654.75</v>
+        <v>2998295004.7</v>
       </c>
       <c r="AP3" t="n">
-        <v>733625038.42</v>
+        <v>1144624373.85</v>
       </c>
       <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
       <c r="AS3" t="n">
-        <v>78636072.28</v>
+        <v>71504724.83</v>
       </c>
       <c r="AT3" t="n">
-        <v>157808397.87</v>
-      </c>
-      <c r="AU3" t="inlineStr"/>
+        <v>662616952.01</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
       <c r="AV3" t="n">
-        <v>47702656.62</v>
+        <v>502211599.45</v>
       </c>
       <c r="AW3" t="n">
-        <v>110105741.25</v>
+        <v>160405352.56</v>
       </c>
       <c r="AX3" t="n">
-        <v>10121697.55</v>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+        <v>10132457</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>512344056.45</v>
+      </c>
       <c r="AZ3" t="n">
-        <v>432018591.53</v>
+        <v>236803100</v>
       </c>
       <c r="BA3" t="n">
-        <v>4519828.31</v>
+        <v>10395621.02</v>
       </c>
       <c r="BB3" t="n">
-        <v>4519828.31</v>
-      </c>
-      <c r="BC3" t="inlineStr"/>
+        <v>10395621.02</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
       <c r="BD3" t="n">
-        <v>50520450.88</v>
+        <v>153171518.99</v>
       </c>
       <c r="BE3" t="n">
-        <v>-278514729.26</v>
+        <v>-422166956.84</v>
       </c>
       <c r="BF3" t="n">
-        <v>329035180.14</v>
-      </c>
-      <c r="BG3" t="inlineStr"/>
+        <v>575338475.83</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>172212.4</v>
+      </c>
       <c r="BH3" t="n">
-        <v>110288052.23</v>
+        <v>113591525.63</v>
       </c>
       <c r="BI3" t="n">
-        <v>172265301.33</v>
+        <v>318052977.93</v>
       </c>
       <c r="BJ3" t="n">
-        <v>46481826.58</v>
+        <v>143521759.87</v>
       </c>
       <c r="BK3" t="n">
-        <v>2140827616.33</v>
-      </c>
-      <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="inlineStr"/>
-      <c r="BN3" t="inlineStr"/>
-      <c r="BO3" t="inlineStr"/>
+        <v>1853670630.85</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>24687737.51</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>163961528.06</v>
+      </c>
       <c r="BP3" t="n">
-        <v>30031414.27</v>
+        <v>97574196.09999999</v>
       </c>
       <c r="BQ3" t="n">
-        <v>50343051.37</v>
-      </c>
-      <c r="BR3" t="inlineStr"/>
+        <v>36949072.95</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>36949072.95</v>
+      </c>
       <c r="BS3" t="inlineStr"/>
-      <c r="BT3" t="inlineStr"/>
+      <c r="BT3" t="n">
+        <v>0</v>
+      </c>
       <c r="BU3" t="n">
-        <v>1380170179.98</v>
+        <v>920944252</v>
       </c>
       <c r="BV3" t="n">
-        <v>39799554.21</v>
+        <v>43321282.4</v>
       </c>
       <c r="BW3" t="n">
-        <v>256706725.95</v>
+        <v>240880565.69</v>
       </c>
       <c r="BX3" t="n">
-        <v>-291155736.71</v>
+        <v>-314825572.33</v>
       </c>
       <c r="BY3" t="n">
-        <v>547862462.66</v>
+        <v>555706138.02</v>
       </c>
       <c r="BZ3" t="n">
-        <v>383776690.55</v>
+        <v>489313524.2</v>
       </c>
       <c r="CA3" t="n">
-        <v>16674448</v>
+        <v>16436168</v>
       </c>
       <c r="CB3" t="n">
-        <v>367102242.55</v>
+        <v>472877356.2</v>
       </c>
       <c r="CC3" t="n">
-        <v>349322990.42</v>
+        <v>470600791.54</v>
       </c>
       <c r="CD3" t="n">
-        <v>17779252.13</v>
+        <v>2276564.66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>792058500</v>
@@ -2239,46 +2254,42 @@
         <v>792058500</v>
       </c>
       <c r="D4" t="n">
-        <v>350262885.44</v>
+        <v>318737557.12</v>
       </c>
       <c r="E4" t="n">
-        <v>823140241.64</v>
+        <v>685839799.67</v>
       </c>
       <c r="F4" t="n">
-        <v>1538549712.16</v>
+        <v>1619818899.36</v>
       </c>
       <c r="G4" t="n">
-        <v>2372085574.82</v>
+        <v>2310178527.34</v>
       </c>
       <c r="H4" t="n">
-        <v>525645455.64</v>
+        <v>1014399426.31</v>
       </c>
       <c r="I4" t="n">
-        <v>1538549712.16</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
+        <v>1619818899.36</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>1548945333.18</v>
+        <v>1624338727.67</v>
       </c>
       <c r="L4" t="n">
-        <v>1636977784.96</v>
+        <v>1702588727.67</v>
       </c>
       <c r="M4" t="n">
-        <v>1558592307.71</v>
+        <v>1633165253.24</v>
       </c>
       <c r="N4" t="n">
-        <v>9646974.529999999</v>
+        <v>8826525.57</v>
       </c>
       <c r="O4" t="n">
-        <v>1548945333.18</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
+        <v>1624338727.67</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>536999877.42</v>
+        <v>539748081.6</v>
       </c>
       <c r="R4" t="n">
         <v>80999419.73</v>
@@ -2289,190 +2300,160 @@
       <c r="T4" t="n">
         <v>792058500</v>
       </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>1439702696.99</v>
+        <v>1241287401.51</v>
       </c>
       <c r="W4" t="n">
-        <v>111677521.78</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
+        <v>114859211.49</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>6935213.17</v>
+        <v>126451.87</v>
       </c>
       <c r="Z4" t="n">
-        <v>16709856.83</v>
+        <v>36482759.62</v>
       </c>
       <c r="AA4" t="n">
-        <v>88032451.78</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
+        <v>78250000</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>88032451.78</v>
+        <v>78250000</v>
       </c>
       <c r="AD4" t="n">
-        <v>1328025175.21</v>
+        <v>1126428190.02</v>
       </c>
       <c r="AE4" t="n">
-        <v>4923951.9</v>
+        <v>1700000</v>
       </c>
       <c r="AF4" t="n">
-        <v>735107789.86</v>
+        <v>607589799.67</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>735107789.86</v>
+        <v>607589799.67</v>
       </c>
       <c r="AI4" t="n">
-        <v>226323.85</v>
+        <v>221603.85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>516803430.97</v>
+        <v>459335195.1</v>
       </c>
       <c r="AK4" t="n">
-        <v>38940006.97</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
+        <v>38482826.87</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
-        <v>7930534.13</v>
+        <v>6010260.76</v>
       </c>
       <c r="AN4" t="n">
-        <v>469932889.87</v>
+        <v>414842107.47</v>
       </c>
       <c r="AO4" t="n">
-        <v>2998295004.7</v>
+        <v>2874452654.75</v>
       </c>
       <c r="AP4" t="n">
-        <v>1144624373.85</v>
+        <v>733625038.42</v>
       </c>
       <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>71504724.83</v>
+        <v>78636072.28</v>
       </c>
       <c r="AT4" t="n">
-        <v>662616952.01</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
+        <v>157808397.87</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>502211599.45</v>
+        <v>47702656.62</v>
       </c>
       <c r="AW4" t="n">
-        <v>160405352.56</v>
+        <v>110105741.25</v>
       </c>
       <c r="AX4" t="n">
-        <v>10132457</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>512344056.45</v>
-      </c>
+        <v>10121697.55</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="n">
-        <v>236803100</v>
+        <v>432018591.53</v>
       </c>
       <c r="BA4" t="n">
-        <v>10395621.02</v>
+        <v>4519828.31</v>
       </c>
       <c r="BB4" t="n">
-        <v>10395621.02</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
+        <v>4519828.31</v>
+      </c>
+      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
-        <v>153171518.99</v>
+        <v>50520450.88</v>
       </c>
       <c r="BE4" t="n">
-        <v>-422166956.84</v>
+        <v>-278514729.26</v>
       </c>
       <c r="BF4" t="n">
-        <v>575338475.83</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>172212.4</v>
-      </c>
+        <v>329035180.14</v>
+      </c>
+      <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="n">
-        <v>113591525.63</v>
+        <v>110288052.23</v>
       </c>
       <c r="BI4" t="n">
-        <v>318052977.93</v>
+        <v>172265301.33</v>
       </c>
       <c r="BJ4" t="n">
-        <v>143521759.87</v>
+        <v>46481826.58</v>
       </c>
       <c r="BK4" t="n">
-        <v>1853670630.85</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>24687737.51</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>163961528.06</v>
-      </c>
+        <v>2140827616.33</v>
+      </c>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
+      <c r="BO4" t="inlineStr"/>
       <c r="BP4" t="n">
-        <v>97574196.09999999</v>
+        <v>30031414.27</v>
       </c>
       <c r="BQ4" t="n">
-        <v>36949072.95</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>36949072.95</v>
-      </c>
+        <v>50343051.37</v>
+      </c>
+      <c r="BR4" t="inlineStr"/>
       <c r="BS4" t="inlineStr"/>
-      <c r="BT4" t="n">
-        <v>0</v>
-      </c>
+      <c r="BT4" t="inlineStr"/>
       <c r="BU4" t="n">
-        <v>920944252</v>
+        <v>1380170179.98</v>
       </c>
       <c r="BV4" t="n">
-        <v>43321282.4</v>
+        <v>39799554.21</v>
       </c>
       <c r="BW4" t="n">
-        <v>240880565.69</v>
+        <v>256706725.95</v>
       </c>
       <c r="BX4" t="n">
-        <v>-314825572.33</v>
+        <v>-291155736.71</v>
       </c>
       <c r="BY4" t="n">
-        <v>555706138.02</v>
+        <v>547862462.66</v>
       </c>
       <c r="BZ4" t="n">
-        <v>489313524.2</v>
+        <v>383776690.55</v>
       </c>
       <c r="CA4" t="n">
-        <v>16436168</v>
+        <v>16674448</v>
       </c>
       <c r="CB4" t="n">
-        <v>472877356.2</v>
+        <v>367102242.55</v>
       </c>
       <c r="CC4" t="n">
-        <v>470600791.54</v>
+        <v>349322990.42</v>
       </c>
       <c r="CD4" t="n">
-        <v>2276564.66</v>
+        <v>17779252.13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>792058500</v>
@@ -2481,241 +2462,411 @@
         <v>792058500</v>
       </c>
       <c r="D5" t="n">
-        <v>603185245.27</v>
+        <v>313569459.95</v>
       </c>
       <c r="E5" t="n">
-        <v>963062942.91</v>
+        <v>586125708.89</v>
       </c>
       <c r="F5" t="n">
-        <v>1827055564.53</v>
+        <v>1204986028.88</v>
       </c>
       <c r="G5" t="n">
-        <v>2800426665.36</v>
+        <v>1796061096.03</v>
       </c>
       <c r="H5" t="n">
-        <v>1302878493.91</v>
+        <v>562310758.33</v>
       </c>
       <c r="I5" t="n">
-        <v>1827055564.53</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
+        <v>1204986028.88</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>1837363722.45</v>
+        <v>1209935387.14</v>
       </c>
       <c r="L5" t="n">
-        <v>1927613722.45</v>
+        <v>1280785387.14</v>
       </c>
       <c r="M5" t="n">
-        <v>1877459254.54</v>
+        <v>1218604669.18</v>
       </c>
       <c r="N5" t="n">
-        <v>40095532.09</v>
+        <v>8669282.039999999</v>
       </c>
       <c r="O5" t="n">
-        <v>1837363722.45</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
+        <v>1209935387.14</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>812449980.76</v>
-      </c>
-      <c r="R5" t="n">
-        <v>103269821.12</v>
-      </c>
+        <v>119155929.9</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
         <v>792058500</v>
       </c>
       <c r="T5" t="n">
         <v>792058500</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>1673797713.11</v>
+        <v>1167687754.35</v>
       </c>
       <c r="W5" t="n">
-        <v>120440338.7</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
+        <v>105872093.53</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>14385829.85</v>
+        <v>1021907.98</v>
       </c>
       <c r="Z5" t="n">
-        <v>15804508.85</v>
+        <v>34000185.55</v>
       </c>
       <c r="AA5" t="n">
-        <v>90250000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
+        <v>70850000</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>90250000</v>
+        <v>70850000</v>
       </c>
       <c r="AD5" t="n">
-        <v>1553357374.41</v>
+        <v>1061815660.82</v>
       </c>
       <c r="AE5" t="n">
-        <v>1301000</v>
+        <v>641173.4</v>
       </c>
       <c r="AF5" t="n">
-        <v>872812942.91</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
+        <v>515275708.89</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>872812942.91</v>
+        <v>515275708.89</v>
       </c>
       <c r="AI5" t="n">
-        <v>359522.74</v>
+        <v>523985.42</v>
       </c>
       <c r="AJ5" t="n">
-        <v>609893094.5</v>
+        <v>434976008.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>52244563.53</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
+        <v>39505193.84</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
-        <v>9917152.619999999</v>
+        <v>4613924.82</v>
       </c>
       <c r="AN5" t="n">
-        <v>547731378.35</v>
+        <v>390856889.4</v>
       </c>
       <c r="AO5" t="n">
-        <v>3551256967.65</v>
+        <v>2386292423.53</v>
       </c>
       <c r="AP5" t="n">
-        <v>695021099.33</v>
+        <v>762166004.38</v>
       </c>
       <c r="AQ5" t="n">
-        <v>23665787.5</v>
+        <v>1000000.02</v>
       </c>
       <c r="AR5" t="n">
-        <v>620319.39</v>
+        <v>98371.14999999999</v>
       </c>
       <c r="AS5" t="n">
-        <v>68446098.11</v>
+        <v>125448113.68</v>
       </c>
       <c r="AT5" t="n">
-        <v>140947660.22</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
+        <v>145531388.15</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>140947660.22</v>
+        <v>42712749.75</v>
       </c>
       <c r="AW5" t="n">
-        <v>140947660.22</v>
+        <v>102818638.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>5728742.53</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>5728742.53</v>
-      </c>
+        <v>10154577.39</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="n">
-        <v>236490100</v>
+        <v>422191100</v>
       </c>
       <c r="BA5" t="n">
-        <v>10308157.92</v>
+        <v>4949358.26</v>
       </c>
       <c r="BB5" t="n">
-        <v>10308157.92</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
+        <v>4949358.26</v>
+      </c>
+      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="n">
-        <v>208814233.66</v>
+        <v>52793095.73</v>
       </c>
       <c r="BE5" t="n">
-        <v>-368193407.67</v>
+        <v>-263994552.34</v>
       </c>
       <c r="BF5" t="n">
-        <v>577007641.33</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0</v>
-      </c>
+        <v>316787648.07</v>
+      </c>
+      <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="n">
-        <v>115049053.36</v>
+        <v>88883016.92</v>
       </c>
       <c r="BI5" t="n">
-        <v>318436828.1</v>
+        <v>172265301.33</v>
       </c>
       <c r="BJ5" t="n">
-        <v>143521759.87</v>
+        <v>55639329.82</v>
       </c>
       <c r="BK5" t="n">
-        <v>2856235868.32</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>74216262.59999999</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>428077500</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>19435145.68</v>
-      </c>
+        <v>1624126419.15</v>
+      </c>
+      <c r="BL5" t="inlineStr"/>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
+      <c r="BO5" t="inlineStr"/>
       <c r="BP5" t="n">
-        <v>147491469.31</v>
+        <v>15754991.57</v>
       </c>
       <c r="BQ5" t="n">
-        <v>70393240.44</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>70378727.17</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>26158324.47</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>14513.27</v>
-      </c>
+        <v>5607358.59</v>
+      </c>
+      <c r="BR5" t="inlineStr"/>
+      <c r="BS5" t="inlineStr"/>
+      <c r="BT5" t="inlineStr"/>
       <c r="BU5" t="n">
-        <v>1436031779.79</v>
+        <v>1087125745.32</v>
       </c>
       <c r="BV5" t="n">
-        <v>54219739.39</v>
+        <v>38237638.46</v>
       </c>
       <c r="BW5" t="n">
-        <v>326188720.07</v>
+        <v>187805300.27</v>
       </c>
       <c r="BX5" t="n">
-        <v>-227602552.87</v>
+        <v>-277247227.04</v>
       </c>
       <c r="BY5" t="n">
-        <v>553791272.9400001</v>
+        <v>465052527.31</v>
       </c>
       <c r="BZ5" t="n">
-        <v>374398273.64</v>
+        <v>289595384.94</v>
       </c>
       <c r="CA5" t="n">
-        <v>14520576</v>
+        <v>17039136</v>
       </c>
       <c r="CB5" t="n">
-        <v>359877697.64</v>
+        <v>272556248.94</v>
       </c>
       <c r="CC5" t="n">
-        <v>18792030.26</v>
+        <v>259429791.43</v>
       </c>
       <c r="CD5" t="n">
-        <v>360520813.06</v>
+        <v>13126457.51</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>792058500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>792058500</v>
+      </c>
+      <c r="D6" t="n">
+        <v>99307466.95</v>
+      </c>
+      <c r="E6" t="n">
+        <v>440218853.14</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1120736161.3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1567665782.98</v>
+      </c>
+      <c r="H6" t="n">
+        <v>476946330.77</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1120736161.3</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>1127446929.84</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1190896929.84</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1127446929.84</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>1127446929.84</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>46031264.57</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>792058500</v>
+      </c>
+      <c r="T6" t="n">
+        <v>792058500</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>960088030.65</v>
+      </c>
+      <c r="W6" t="n">
+        <v>104293808.71</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="n">
+        <v>2228841.73</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>38614966.98</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>63450000</v>
+      </c>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>63450000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>855794221.9400001</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>5639244.82</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>376768853.14</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="n">
+        <v>376768853.14</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>180883.9</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>370749668.89</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>39873683.02</v>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="n">
+        <v>4781185.39</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>326094800.48</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>2087534960.49</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>754794407.78</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>53303.93</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>82892645.53</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>146893736.34</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="n">
+        <v>40031021.94</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>106862714.4</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>9621683.01</v>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="n">
+        <v>423311400</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>6710768.54</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>6710768.54</v>
+      </c>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="n">
+        <v>85310870.43000001</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>-265797229.85</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>351108100.28</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>8071813.57</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>89248755.27</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>172265301.33</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>81522230.11</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1332740552.71</v>
+      </c>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="n">
+        <v>13414572</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>2004286.43</v>
+      </c>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="inlineStr"/>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="n">
+        <v>757807628.27</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>41045688.18</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>160937743.64</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>-264889835.83</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>425827579.47</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>357530634.19</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>16619248</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>340911386.19</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>329200910.93</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>11710475.26</v>
       </c>
     </row>
   </sheetData>
@@ -2729,7 +2880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:BC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2943,490 +3094,743 @@
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>Cash Flowsfromusedin Operating Activities Direct</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>Taxes Refund Paid Direct</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>Interest Received Direct</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>Interest Paid Direct</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>Dividends Paid Direct</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>Classesof Cash Payments</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>Other Cash Paymentsfrom Operating Activities</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>Paymentson Behalfof Employees</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Paymentsto Suppliersfor Goodsand Services</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>Classesof Cash Receiptsfrom Operating Activities</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>Other Cash Receiptsfrom Operating Activities</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>Receiptsfrom Customers</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>22212399.34</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-552220000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>452270000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-741716.7</v>
-      </c>
-      <c r="F2" t="n">
-        <v>248510856.27</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="H2" t="n">
-        <v>340989178.69</v>
-      </c>
-      <c r="I2" t="n">
-        <v>4539.83</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-92482862.23999999</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-126784890.89</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
-        <v>-26834890.89</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>-99950000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-99950000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-552220000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>452270000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>11347912.61</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="n">
-        <v>12089629.31</v>
-      </c>
-      <c r="V2" t="n">
-        <v>13089629.31</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>-506115000</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>-59750910.86</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>-12313737.43</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>-1000000</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="n">
-        <v>-741716.7</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="n">
-        <v>-741716.7</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>22954116.04</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>50578688.09</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-50235485.88</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>21485745.79</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>51488291.93</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>27840136.25</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>27069007.64</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>6630126.19</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>191647.74</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>6438478.45</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>5974142.51</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="n">
-        <v>-420749395.23</v>
+        <v>-4000000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="n">
+        <v>261280.44</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="n">
+        <v>11351.46</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-7895225.06</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="n">
+        <v>206787628.94</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>-24805604.6</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>-2451141607.92</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>-459085697.48</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>-67639207.25</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>-1924416703.19</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>2682734841.46</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>276946857.79</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>2405787983.67</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>177850967.99</v>
+        <v>134336050.36</v>
       </c>
       <c r="C3" t="n">
-        <v>-793940594.9299999</v>
+        <v>-1056189405.07</v>
       </c>
       <c r="D3" t="n">
-        <v>656720000</v>
+        <v>920360000</v>
       </c>
       <c r="E3" t="n">
-        <v>-3305633.67</v>
+        <v>-299745.23</v>
       </c>
       <c r="F3" t="n">
-        <v>340989178.69</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.05</v>
-      </c>
+        <v>308915828.15</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>308915828.15</v>
+        <v>359877697.64</v>
       </c>
       <c r="I3" t="n">
-        <v>-307.49</v>
+        <v>-28869.01</v>
       </c>
       <c r="J3" t="n">
-        <v>32073658.03</v>
+        <v>-50933000.48</v>
       </c>
       <c r="K3" t="n">
-        <v>-171806997.91</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-353545.41</v>
-      </c>
+        <v>-193235557.96</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>-34232857.57</v>
+        <v>-57406152.89</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>-137220594.93</v>
+        <v>-135829405.07</v>
       </c>
       <c r="P3" t="n">
-        <v>-137220594.93</v>
+        <v>-135829405.07</v>
       </c>
       <c r="Q3" t="n">
-        <v>-793940594.9299999</v>
+        <v>-1056189405.07</v>
       </c>
       <c r="R3" t="n">
-        <v>656720000</v>
+        <v>920360000</v>
       </c>
       <c r="S3" t="n">
-        <v>22724054.28</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
+        <v>7666761.89</v>
+      </c>
+      <c r="T3" t="n">
+        <v>39077407.21</v>
+      </c>
       <c r="U3" t="n">
-        <v>26029000</v>
+        <v>-31233847.69</v>
       </c>
       <c r="V3" t="n">
-        <v>26029000</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+        <v>110096912.15</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-141330759.84</v>
+      </c>
+      <c r="X3" t="n">
+        <v>108104.01</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>108104.01</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
       <c r="AA3" t="n">
-        <v>-3304945.72</v>
+        <v>-284901.64</v>
       </c>
       <c r="AB3" t="n">
-        <v>687.95</v>
+        <v>14843.59</v>
       </c>
       <c r="AC3" t="n">
-        <v>-3305633.67</v>
+        <v>-299745.23</v>
       </c>
       <c r="AD3" t="n">
-        <v>181156601.66</v>
+        <v>134635795.59</v>
       </c>
       <c r="AE3" t="n">
-        <v>17594204.63</v>
+        <v>286871573.48</v>
       </c>
       <c r="AF3" t="n">
-        <v>579844.35</v>
+        <v>-2153278.74</v>
       </c>
       <c r="AG3" t="n">
-        <v>-77387924.56999999</v>
+        <v>-131194171.51</v>
       </c>
       <c r="AH3" t="n">
-        <v>-13672165.86</v>
+        <v>27560073.58</v>
       </c>
       <c r="AI3" t="n">
-        <v>108074450.71</v>
+        <v>392658950.15</v>
       </c>
       <c r="AJ3" t="n">
-        <v>171901782.22</v>
+        <v>-102169150.73</v>
       </c>
       <c r="AK3" t="n">
-        <v>38139654.11</v>
+        <v>57200734.75</v>
       </c>
       <c r="AL3" t="n">
-        <v>1379147.28</v>
+        <v>1166153.78</v>
       </c>
       <c r="AM3" t="n">
-        <v>36760506.83</v>
+        <v>56034580.97</v>
       </c>
       <c r="AN3" t="n">
-        <v>-35822693.17</v>
-      </c>
-      <c r="AO3" t="inlineStr"/>
+        <v>-1420832.85</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>67124.7</v>
+      </c>
       <c r="AP3" t="n">
-        <v>-194541.84</v>
+        <v>1024248.53</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1722603.06</v>
+        <v>-300862226.17</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>134635795.59</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-19306182.02</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>-1590353232.68</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>-1010425326.53</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>-59421158.11</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-520506748.04</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1744295210.29</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1083267010.87</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>661028199.42</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>134336050.36</v>
+        <v>177850967.99</v>
       </c>
       <c r="C4" t="n">
-        <v>-1056189405.07</v>
+        <v>-793940594.9299999</v>
       </c>
       <c r="D4" t="n">
-        <v>920360000</v>
+        <v>656720000</v>
       </c>
       <c r="E4" t="n">
-        <v>-299745.23</v>
+        <v>-3305633.67</v>
       </c>
       <c r="F4" t="n">
+        <v>340989178.69</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H4" t="n">
         <v>308915828.15</v>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="n">
-        <v>359877697.64</v>
-      </c>
       <c r="I4" t="n">
-        <v>-28869.01</v>
+        <v>-307.49</v>
       </c>
       <c r="J4" t="n">
-        <v>-50933000.48</v>
+        <v>32073658.03</v>
       </c>
       <c r="K4" t="n">
-        <v>-193235557.96</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
+        <v>-171806997.91</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-353545.41</v>
+      </c>
       <c r="M4" t="n">
-        <v>-57406152.89</v>
+        <v>-34232857.57</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>-135829405.07</v>
+        <v>-137220594.93</v>
       </c>
       <c r="P4" t="n">
-        <v>-135829405.07</v>
+        <v>-137220594.93</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1056189405.07</v>
+        <v>-793940594.9299999</v>
       </c>
       <c r="R4" t="n">
-        <v>920360000</v>
+        <v>656720000</v>
       </c>
       <c r="S4" t="n">
-        <v>7666761.89</v>
-      </c>
-      <c r="T4" t="n">
-        <v>39077407.21</v>
-      </c>
+        <v>22724054.28</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>-31233847.69</v>
+        <v>26029000</v>
       </c>
       <c r="V4" t="n">
-        <v>110096912.15</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-141330759.84</v>
-      </c>
-      <c r="X4" t="n">
-        <v>108104.01</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>108104.01</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
+        <v>26029000</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>-284901.64</v>
+        <v>-3304945.72</v>
       </c>
       <c r="AB4" t="n">
-        <v>14843.59</v>
+        <v>687.95</v>
       </c>
       <c r="AC4" t="n">
-        <v>-299745.23</v>
+        <v>-3305633.67</v>
       </c>
       <c r="AD4" t="n">
-        <v>134635795.59</v>
+        <v>181156601.66</v>
       </c>
       <c r="AE4" t="n">
-        <v>286871573.48</v>
+        <v>17594204.63</v>
       </c>
       <c r="AF4" t="n">
-        <v>-2153278.74</v>
+        <v>579844.35</v>
       </c>
       <c r="AG4" t="n">
-        <v>-131194171.51</v>
+        <v>-77387924.56999999</v>
       </c>
       <c r="AH4" t="n">
-        <v>27560073.58</v>
+        <v>-13672165.86</v>
       </c>
       <c r="AI4" t="n">
-        <v>392658950.15</v>
+        <v>108074450.71</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-102169150.73</v>
+        <v>171901782.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>57200734.75</v>
+        <v>38139654.11</v>
       </c>
       <c r="AL4" t="n">
-        <v>1166153.78</v>
+        <v>1379147.28</v>
       </c>
       <c r="AM4" t="n">
-        <v>56034580.97</v>
+        <v>36760506.83</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1420832.85</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>67124.7</v>
-      </c>
+        <v>-35822693.17</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>1024248.53</v>
+        <v>-194541.84</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-300862226.17</v>
+        <v>1722603.06</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>181156601.66</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-14092471</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="n">
+        <v>-1119364329.45</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>-603607589.61</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>-49915616.81</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-465841123.03</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1314613402.11</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>658721988.8099999</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>655891413.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>189928588.12</v>
+        <v>22212399.34</v>
       </c>
       <c r="C5" t="n">
-        <v>-1039940000</v>
+        <v>-552220000</v>
       </c>
       <c r="D5" t="n">
-        <v>1210310000</v>
+        <v>452270000</v>
       </c>
       <c r="E5" t="n">
-        <v>-16859040.82</v>
+        <v>-741716.7</v>
       </c>
       <c r="F5" t="n">
-        <v>359877697.64</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
+        <v>248510856.27</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.01</v>
+      </c>
       <c r="H5" t="n">
-        <v>379222636.69</v>
+        <v>340989178.69</v>
       </c>
       <c r="I5" t="n">
-        <v>-217228.51</v>
+        <v>4539.83</v>
       </c>
       <c r="J5" t="n">
-        <v>-19127710.54</v>
+        <v>-92482862.23999999</v>
       </c>
       <c r="K5" t="n">
-        <v>-395495910.86</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-506115000</v>
-      </c>
+        <v>-126784890.89</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>-59750910.86</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-59750910.86</v>
-      </c>
+        <v>-26834890.89</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>170370000</v>
+        <v>-99950000</v>
       </c>
       <c r="P5" t="n">
-        <v>170370000</v>
+        <v>-99950000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1039940000</v>
+        <v>-552220000</v>
       </c>
       <c r="R5" t="n">
-        <v>1210310000</v>
+        <v>452270000</v>
       </c>
       <c r="S5" t="n">
-        <v>169580571.38</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-12313737.43</v>
-      </c>
+        <v>11347912.61</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>198492069.19</v>
+        <v>12089629.31</v>
       </c>
       <c r="V5" t="n">
-        <v>202492069.19</v>
+        <v>13089629.31</v>
       </c>
       <c r="W5" t="n">
-        <v>-4000000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
+        <v>-1000000</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>-16597760.38</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>261280.44</v>
-      </c>
+        <v>-741716.7</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>-16859040.82</v>
+        <v>-741716.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>206787628.94</v>
+        <v>22954116.04</v>
       </c>
       <c r="AE5" t="n">
-        <v>124516036.62</v>
+        <v>50578688.09</v>
       </c>
       <c r="AF5" t="n">
-        <v>2780985.33</v>
+        <v>-50235485.88</v>
       </c>
       <c r="AG5" t="n">
-        <v>169201687.27</v>
+        <v>21485745.79</v>
       </c>
       <c r="AH5" t="n">
-        <v>89890100.27</v>
+        <v>51488291.93</v>
       </c>
       <c r="AI5" t="n">
-        <v>-137356736.25</v>
+        <v>27840136.25</v>
       </c>
       <c r="AJ5" t="n">
-        <v>61342311.16</v>
+        <v>27069007.64</v>
       </c>
       <c r="AK5" t="n">
-        <v>50601805.37</v>
+        <v>6630126.19</v>
       </c>
       <c r="AL5" t="n">
-        <v>982289.91</v>
+        <v>191647.74</v>
       </c>
       <c r="AM5" t="n">
-        <v>49619515.46</v>
+        <v>6438478.45</v>
       </c>
       <c r="AN5" t="n">
-        <v>-12422572.5</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>11351.46</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-7895225.06</v>
-      </c>
+        <v>5941262.67</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>-55912187.63</v>
-      </c>
+        <v>-420749395.23</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>22954116.04</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-9334757.16</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="n">
+        <v>-1441494967.84</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-925916524.36</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-44982413</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-470596030.48</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1473783841.03</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>833778573.28</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>640005267.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>261364726.53</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-706170000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>560770000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-9534433.67</v>
+      </c>
+      <c r="F6" t="n">
+        <v>327125525.74</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>248510856.27</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-2958.86</v>
+      </c>
+      <c r="J6" t="n">
+        <v>78617628.33</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-169162370.85</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>-23762370.85</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>-145400000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-145400000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-706170000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>560770000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-23119161.02</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-14000000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>415272.65</v>
+      </c>
+      <c r="V6" t="n">
+        <v>415272.65</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>-9534433.67</v>
+      </c>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>-9534433.67</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>270899160.2</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>330144718.24</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>47170249.58</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-71654557.2</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>3381813.99</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>351247211.87</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>23300582.34</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1922519.59</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>119842.08</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1802677.51</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-33115862.35</v>
+      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>-73124665.33</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3439,7 +3843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EO2"/>
+  <dimension ref="A1:EL2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3590,580 +3994,565 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>exDividendDate</t>
+          <t>beta</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>payoutRatio</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>fiveYearAvgDividendYield</t>
+          <t>regularMarketVolume</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>beta</t>
+          <t>averageVolume</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>averageVolume10days</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>regularMarketVolume</t>
+          <t>averageDailyVolume10Day</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>averageVolume</t>
+          <t>bid</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>averageVolume10days</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>averageDailyVolume10Day</t>
+          <t>bidSize</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>bid</t>
+          <t>askSize</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>marketCap</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>bidSize</t>
+          <t>nonDilutedMarketCap</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>askSize</t>
+          <t>fiftyTwoWeekLow</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>marketCap</t>
+          <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>nonDilutedMarketCap</t>
+          <t>allTimeHigh</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekLow</t>
+          <t>allTimeLow</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekHigh</t>
+          <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>allTimeHigh</t>
+          <t>fiftyDayAverage</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>allTimeLow</t>
+          <t>twoHundredDayAverage</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>priceToSalesTrailing12Months</t>
+          <t>trailingAnnualDividendRate</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>fiftyDayAverage</t>
+          <t>trailingAnnualDividendYield</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>twoHundredDayAverage</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendRate</t>
+          <t>tradeable</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendYield</t>
+          <t>enterpriseValue</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>profitMargins</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>tradeable</t>
+          <t>floatShares</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>enterpriseValue</t>
+          <t>sharesOutstanding</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>profitMargins</t>
+          <t>heldPercentInsiders</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>floatShares</t>
+          <t>heldPercentInstitutions</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>sharesOutstanding</t>
+          <t>impliedSharesOutstanding</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>heldPercentInsiders</t>
+          <t>bookValue</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>heldPercentInstitutions</t>
+          <t>priceToBook</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>impliedSharesOutstanding</t>
+          <t>lastFiscalYearEnd</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>bookValue</t>
+          <t>nextFiscalYearEnd</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>priceToBook</t>
+          <t>mostRecentQuarter</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>lastFiscalYearEnd</t>
+          <t>netIncomeToCommon</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>nextFiscalYearEnd</t>
+          <t>trailingEps</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
         <is>
-          <t>mostRecentQuarter</t>
+          <t>pegRatio</t>
         </is>
       </c>
       <c r="BP1" t="inlineStr">
         <is>
-          <t>netIncomeToCommon</t>
+          <t>lastSplitFactor</t>
         </is>
       </c>
       <c r="BQ1" t="inlineStr">
         <is>
-          <t>trailingEps</t>
+          <t>lastSplitDate</t>
         </is>
       </c>
       <c r="BR1" t="inlineStr">
         <is>
-          <t>pegRatio</t>
+          <t>enterpriseToRevenue</t>
         </is>
       </c>
       <c r="BS1" t="inlineStr">
         <is>
-          <t>lastSplitFactor</t>
+          <t>enterpriseToEbitda</t>
         </is>
       </c>
       <c r="BT1" t="inlineStr">
         <is>
-          <t>lastSplitDate</t>
+          <t>52WeekChange</t>
         </is>
       </c>
       <c r="BU1" t="inlineStr">
         <is>
-          <t>enterpriseToRevenue</t>
+          <t>SandP52WeekChange</t>
         </is>
       </c>
       <c r="BV1" t="inlineStr">
         <is>
-          <t>enterpriseToEbitda</t>
+          <t>lastDividendValue</t>
         </is>
       </c>
       <c r="BW1" t="inlineStr">
         <is>
-          <t>52WeekChange</t>
+          <t>lastDividendDate</t>
         </is>
       </c>
       <c r="BX1" t="inlineStr">
         <is>
-          <t>SandP52WeekChange</t>
+          <t>quoteType</t>
         </is>
       </c>
       <c r="BY1" t="inlineStr">
         <is>
-          <t>lastDividendValue</t>
+          <t>currentPrice</t>
         </is>
       </c>
       <c r="BZ1" t="inlineStr">
         <is>
-          <t>lastDividendDate</t>
+          <t>recommendationKey</t>
         </is>
       </c>
       <c r="CA1" t="inlineStr">
         <is>
-          <t>quoteType</t>
+          <t>totalCash</t>
         </is>
       </c>
       <c r="CB1" t="inlineStr">
         <is>
-          <t>currentPrice</t>
+          <t>totalCashPerShare</t>
         </is>
       </c>
       <c r="CC1" t="inlineStr">
         <is>
-          <t>recommendationKey</t>
+          <t>ebitda</t>
         </is>
       </c>
       <c r="CD1" t="inlineStr">
         <is>
-          <t>totalCash</t>
+          <t>totalDebt</t>
         </is>
       </c>
       <c r="CE1" t="inlineStr">
         <is>
-          <t>totalCashPerShare</t>
+          <t>quickRatio</t>
         </is>
       </c>
       <c r="CF1" t="inlineStr">
         <is>
-          <t>ebitda</t>
+          <t>currentRatio</t>
         </is>
       </c>
       <c r="CG1" t="inlineStr">
         <is>
-          <t>totalDebt</t>
+          <t>totalRevenue</t>
         </is>
       </c>
       <c r="CH1" t="inlineStr">
         <is>
-          <t>quickRatio</t>
+          <t>debtToEquity</t>
         </is>
       </c>
       <c r="CI1" t="inlineStr">
         <is>
-          <t>currentRatio</t>
+          <t>revenuePerShare</t>
         </is>
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
-          <t>totalRevenue</t>
+          <t>returnOnAssets</t>
         </is>
       </c>
       <c r="CK1" t="inlineStr">
         <is>
-          <t>debtToEquity</t>
+          <t>returnOnEquity</t>
         </is>
       </c>
       <c r="CL1" t="inlineStr">
         <is>
-          <t>revenuePerShare</t>
+          <t>grossProfits</t>
         </is>
       </c>
       <c r="CM1" t="inlineStr">
         <is>
-          <t>returnOnAssets</t>
+          <t>freeCashflow</t>
         </is>
       </c>
       <c r="CN1" t="inlineStr">
         <is>
-          <t>returnOnEquity</t>
+          <t>operatingCashflow</t>
         </is>
       </c>
       <c r="CO1" t="inlineStr">
         <is>
-          <t>grossProfits</t>
+          <t>revenueGrowth</t>
         </is>
       </c>
       <c r="CP1" t="inlineStr">
         <is>
-          <t>freeCashflow</t>
+          <t>grossMargins</t>
         </is>
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
-          <t>operatingCashflow</t>
+          <t>ebitdaMargins</t>
         </is>
       </c>
       <c r="CR1" t="inlineStr">
         <is>
-          <t>revenueGrowth</t>
+          <t>operatingMargins</t>
         </is>
       </c>
       <c r="CS1" t="inlineStr">
         <is>
-          <t>grossMargins</t>
+          <t>financialCurrency</t>
         </is>
       </c>
       <c r="CT1" t="inlineStr">
         <is>
-          <t>ebitdaMargins</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="CU1" t="inlineStr">
         <is>
-          <t>operatingMargins</t>
+          <t>language</t>
         </is>
       </c>
       <c r="CV1" t="inlineStr">
         <is>
-          <t>financialCurrency</t>
+          <t>region</t>
         </is>
       </c>
       <c r="CW1" t="inlineStr">
         <is>
-          <t>symbol</t>
+          <t>typeDisp</t>
         </is>
       </c>
       <c r="CX1" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>quoteSourceName</t>
         </is>
       </c>
       <c r="CY1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>triggerable</t>
         </is>
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
-          <t>typeDisp</t>
+          <t>customPriceAlertConfidence</t>
         </is>
       </c>
       <c r="DA1" t="inlineStr">
         <is>
-          <t>quoteSourceName</t>
+          <t>marketState</t>
         </is>
       </c>
       <c r="DB1" t="inlineStr">
         <is>
-          <t>triggerable</t>
+          <t>corporateActions</t>
         </is>
       </c>
       <c r="DC1" t="inlineStr">
         <is>
-          <t>customPriceAlertConfidence</t>
+          <t>regularMarketTime</t>
         </is>
       </c>
       <c r="DD1" t="inlineStr">
         <is>
-          <t>marketState</t>
+          <t>exchange</t>
         </is>
       </c>
       <c r="DE1" t="inlineStr">
         <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
       <c r="EL1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4237,7 +4626,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Nanjing Sample Technology Company Limited, together with its subsidiaries, provides visual identification and radio frequency identification (RFID) solutions to intelligent transportation, customs logistics, and other application areas in the People's Republic of China. It offers networked management system of city intelligent traffic, traffic police smart transportation platform scheme, scheme of motor vehicle exhaust supervision system, and expressway smart transportation solutions; and cross border integrated service solutions. The company also provides intelligent prevention and control plan for smart park, smart prevention and control plan for smart communities, and smart prevention and control solutions in public security field; smart city investment services; and IOT financial data supervision services. In addition, it offers network management system of city intelligent traffic and smart security lock services. Further, the company is involved in the intelligent transportation; computer software; Internet of Things (IOT) technology; electronic products; municipal investment; and consultation and investment activities. The company was founded in 2000 and is headquartered in Nanjing, the People's Republic of China. Nanjing Sample Technology Company Limited operates as a subsidiary of Nanjing Sample Technology Group Company Limited.</t>
+          <t>Nanjing Sample Technology Company Limited, together with its subsidiaries, provides visual identification and radio frequency identification (RFID) solutions to intelligent transportation, customs logistics, and other application areas in the People's Republic of China. The company offers smart transportation solutions, such as networked management system of city intelligent traffic, traffic police smart transportation platform scheme, scheme of motor vehicle exhaust supervision system, and expressway smart transportation solutions; and cross border integrated service solutions. It also provides intelligent prevention and control plan for smart park, as well as smart prevention and control plan for smart communities and public security field; smart city investment services. In addition, the company offers IOT financial data management platform; network management system of city intelligent traffic; and smart security lock services. Further, the company is involved in the intelligent transportation, information technology, and municipal investment activities; and provision of computer software, IOT technology, consultation and investment, and electronic products. The company was incorporated in 2000 and is headquartered in Nanjing, the People's Republic of China. Nanjing Sample Technology Company Limited is a subsidiary of Nanjing Sample Technology Group.,Ltd.</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -4245,7 +4634,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Fei  Liu', 'age': 43, 'title': 'CEO &amp; Chairman of the Board', 'yearBorn': 1982, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yonghui  Xu', 'age': 56, 'title': 'VP, CFO &amp; Head of Accounting Department', 'yearBorn': 1969, 'fiscalYear': 2025, 'totalPay': 680521, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Fengkui  Ma', 'age': 50, 'title': 'VP &amp; Executive Director', 'yearBorn': 1975, 'fiscalYear': 2025, 'totalPay': 1132727, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Min  Liu', 'age': 50, 'title': 'VP &amp; Executive Director', 'yearBorn': 1975, 'fiscalYear': 2025, 'totalPay': 784925, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Wong Bing  Ni ACIS, ACS, FCCA, FCPA', 'title': 'Company Secretary', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Fei  Liu', 'age': 43, 'title': 'CEO &amp; Chairman of the Board', 'yearBorn': 1982, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yonghui  Xu', 'age': 56, 'title': 'VP, CFO &amp; Head of Accounting Department', 'yearBorn': 1969, 'fiscalYear': 2025, 'totalPay': 680413, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Fengkui  Ma', 'age': 50, 'title': 'VP &amp; Executive Director', 'yearBorn': 1975, 'fiscalYear': 2025, 'totalPay': 1132549, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Min  Liu', 'age': 50, 'title': 'VP &amp; Executive Director', 'yearBorn': 1975, 'fiscalYear': 2025, 'totalPay': 784801, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Wong Bing  Ni ACIS, ACS, FCCA, FCPA', 'title': 'Company Secretary', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -4268,421 +4657,412 @@
         <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>0.27</v>
+        <v>0.265</v>
       </c>
       <c r="W2" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="X2" t="n">
-        <v>0.25</v>
+        <v>0.237</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.27</v>
+        <v>0.265</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.25</v>
+        <v>0.237</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="AD2" t="n">
+        <v>1.084</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>102000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>102000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>103233</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>22600</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>22600</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>233657248</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>233657257</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>15.539996</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0.46364692</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.314625</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="AZ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>316255456</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>-0.1451</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>171338095</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>229500000</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0.25344</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0.00213</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>792058500</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1.6482023</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0.17898287</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1767139200</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>1798675200</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1767139200</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>-73124656</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>5:3</t>
+        </is>
+      </c>
+      <c r="BQ2" t="n">
+        <v>1530748800</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>-14.871</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>-0.14492756</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>0.2568333</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>0.1138</v>
+      </c>
+      <c r="BW2" t="n">
         <v>1559260800</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="BY2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="CA2" t="n">
+        <v>357530624</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>-21265980</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>440128832</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>1.491</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>1.557</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>503955136</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>39.038</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>-0.00648</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>-0.062340003</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>65034360</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>255196752</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>270899168</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>0.12905</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>-0.0422</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>-0.07348</v>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>1708.HK</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>en-US</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>Delayed Quote</t>
+        </is>
+      </c>
+      <c r="CY2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.089</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>70000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>70000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>102608</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>108150</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>108150</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AO2" t="n">
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DC2" t="n">
+        <v>1781590093</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>finmb_10958252</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DH2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DJ2" t="b">
         <v>0</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>Nanjing Sample Technology Company Limited</t>
+        </is>
+      </c>
+      <c r="DL2" t="b">
         <v>0</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>213855808</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>213855795</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0.241</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>15.539996</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.42435485</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0.316</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0.316625</v>
-      </c>
-      <c r="AZ2" t="n">
+      <c r="DM2" t="n">
+        <v>1086744600000</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>0.030000001</v>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>0.237 - 0.3</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DQ2" t="n">
+        <v>103233</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>0.057999983</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>0.24472566</v>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>0.237 - 0.53</t>
+        </is>
+      </c>
+      <c r="DU2" t="n">
+        <v>-0.23499998</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>-0.4433962</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>-14.492756</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>1745405940</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>1745841600</v>
+      </c>
+      <c r="DZ2" t="b">
+        <v>1</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>SAMPLE TECH</t>
+        </is>
+      </c>
+      <c r="EC2" t="n">
+        <v>-0.009300022999999999</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>-0.03056202</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-0.019625008</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>-0.06237587</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EI2" t="b">
         <v>0</v>
       </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>HKD</t>
-        </is>
-      </c>
-      <c r="BC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>296454016</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>-0.1451</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>171338095</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>229500000</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0.25344</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0.00213</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>792058500</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>1.6480358</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0.1638314</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>1767139200</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1798675200</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>1767139200</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>-73124656</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>5:3</t>
-        </is>
-      </c>
-      <c r="BT2" t="n">
-        <v>1530748800</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0.588</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>-13.94</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0.27449715</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0.1138</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>1559260800</v>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>EQUITY</t>
-        </is>
-      </c>
-      <c r="CB2" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="CD2" t="n">
-        <v>357530624</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>0.451</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>-21265980</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>440128832</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>1.491</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>1.557</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>503955136</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>39.038</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>0.634</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>-0.00648</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>-0.062340003</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>65034360</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>255196752</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>270899168</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>0.532</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>0.12905</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>-0.0422</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>-0.07348</v>
-      </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="CW2" t="inlineStr">
-        <is>
-          <t>1708.HK</t>
-        </is>
-      </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>en-US</t>
-        </is>
-      </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>Delayed Quote</t>
-        </is>
-      </c>
-      <c r="DB2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="DE2" t="n">
-        <v>-0.14725618</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DL2" t="n">
-        <v>1780378857</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>finmb_10958252</t>
-        </is>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DQ2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DS2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>Nanjing Sample Technology Company Limited</t>
-        </is>
-      </c>
-      <c r="DU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>0.25 - 0.27</t>
-        </is>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DX2" t="n">
-        <v>102608</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>0.029000014</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>0.12033201</v>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>0.241 - 0.53</t>
-        </is>
-      </c>
-      <c r="EB2" t="n">
-        <v>-0.25999996</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>-0.490566</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>-25</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>1745405940</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>1745841600</v>
-      </c>
-      <c r="EG2" t="b">
-        <v>1</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>-0.046000004</v>
-      </c>
       <c r="EJ2" t="n">
-        <v>-0.14556962</v>
+        <v>11.320756</v>
       </c>
       <c r="EK2" t="n">
-        <v>-0.04662499</v>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>SAMPLE TECH</t>
-        </is>
-      </c>
-      <c r="EM2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>1086744600000</v>
-      </c>
-      <c r="EO2" t="inlineStr"/>
+        <v>0.295</v>
+      </c>
+      <c r="EL2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
